--- a/modelo_planificacion/Kit_Modelo_Planificacion_CL.xlsx
+++ b/modelo_planificacion/Kit_Modelo_Planificacion_CL.xlsx
@@ -13,13 +13,17 @@
     <sheet name="RACI" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Roles" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Asignación" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Empresas" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Políticas" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="KPIs" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Reuniones" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Decisiones" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Plan" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Organigramas" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Empresas" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Políticas" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="KPIs" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Reuniones" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Decisiones" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Plan" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Organigramas!$A$1:$L$45</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="554">
   <si>
     <t xml:space="preserve">Modelo de planificación corporativo · CL Grupo Industrial</t>
   </si>
@@ -47,7 +51,7 @@
     <t xml:space="preserve">Generado</t>
   </si>
   <si>
-    <t xml:space="preserve">06/10/2026</t>
+    <t xml:space="preserve">07/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Dónde se edita</t>
@@ -95,6 +99,15 @@
     <t xml:space="preserve">roles con titular</t>
   </si>
   <si>
+    <t xml:space="preserve">Organigramas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organigramas as-is y to-be de cada empresa: puesto, persona y dependencias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">puestos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Empresas</t>
   </si>
   <si>
@@ -1002,6 +1015,96 @@
   </si>
   <si>
     <t xml:space="preserve">En amarillo, los huecos por asignar (titular o suplente).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nivel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puesto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Persona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Área</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rol del modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De otra empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depende de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dependencia funcional de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% planificación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To-be</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dirección General</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dirección</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Director/a de Planificación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Responsable de procesos (Functional Lead)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Responsable de dato maestro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Coordinador/a de S&amp;OP e intercompany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Technical Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  Solution Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Responsables de planificación de planta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uno por planta; ver el organigrama de cada empresa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporativo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Responsable de planificación de planta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dependencia jerárquica de corporativo y funcional de la dirección de planta (opción A, pendiente de decisión).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Planificador/a de demanda y cartera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Programador/a de producción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Planificador/a de materiales</t>
   </si>
   <si>
     <t xml:space="preserve">Empresa / planta</t>
@@ -1603,7 +1706,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1737,6 +1840,14 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FFB4532A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1825,7 +1936,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1910,6 +2021,18 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1919,6 +2042,47 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00263A"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAF3FA"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB4532A"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1973,13 +2137,17 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFB4532A"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF244C5A"/>
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2163,7 +2331,7 @@
     <tabColor rgb="FF00263A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:E26"/>
+  <dimension ref="B2:E27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2280,8 +2448,8 @@
         <v>22</v>
       </c>
       <c r="D14" s="7" t="n">
-        <f aca="false">COUNTA(Empresas!A:A)-1</f>
-        <v>7</v>
+        <f aca="false">COUNTA(Organigramas!D:D)-1</f>
+        <v>44</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>23</v>
@@ -2295,8 +2463,8 @@
         <v>25</v>
       </c>
       <c r="D15" s="7" t="n">
-        <f aca="false">COUNTA(Políticas!A:A)-1</f>
-        <v>10</v>
+        <f aca="false">COUNTA(Empresas!A:A)-1</f>
+        <v>7</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>26</v>
@@ -2310,26 +2478,26 @@
         <v>28</v>
       </c>
       <c r="D16" s="7" t="n">
+        <f aca="false">COUNTA(Políticas!A:A)-1</f>
+        <v>10</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="7" t="n">
         <f aca="false">COUNTA(KPIs!A:A)-1</f>
         <v>12</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="E17" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <f aca="false">COUNTA(Reuniones!A:A)-1</f>
-        <v>8</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2340,8 +2508,8 @@
         <v>33</v>
       </c>
       <c r="D18" s="7" t="n">
-        <f aca="false">COUNTIF(Decisiones!F:F,"Abierta")</f>
-        <v>6</v>
+        <f aca="false">COUNTA(Reuniones!A:A)-1</f>
+        <v>8</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>34</v>
@@ -2355,56 +2523,71 @@
         <v>36</v>
       </c>
       <c r="D19" s="7" t="n">
+        <f aca="false">COUNTIF(Decisiones!F:F,"Abierta")</f>
+        <v>6</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="7" t="n">
         <f aca="false">COUNTA(Plan!A:A)-1</f>
         <v>5</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="s">
-        <v>38</v>
+      <c r="E20" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>40</v>
+      <c r="B22" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="10" t="s">
-        <v>41</v>
+      <c r="B23" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="9" t="s">
-        <v>43</v>
+      <c r="B24" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="11" t="s">
-        <v>45</v>
+      <c r="B25" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="12" t="s">
-        <v>47</v>
+      <c r="B26" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -2413,12 +2596,13 @@
     <hyperlink ref="B11" r:id="rId2" location="'RACI'!A1" display="RACI"/>
     <hyperlink ref="B12" r:id="rId3" location="'Roles'!A1" display="Roles"/>
     <hyperlink ref="B13" r:id="rId4" location="'Asignación'!A1" display="Asignación"/>
-    <hyperlink ref="B14" r:id="rId5" location="'Empresas'!A1" display="Empresas"/>
-    <hyperlink ref="B15" r:id="rId6" location="'Políticas'!A1" display="Políticas"/>
-    <hyperlink ref="B16" r:id="rId7" location="'KPIs'!A1" display="KPIs"/>
-    <hyperlink ref="B17" r:id="rId8" location="'Reuniones'!A1" display="Reuniones"/>
-    <hyperlink ref="B18" r:id="rId9" location="'Decisiones'!A1" display="Decisiones"/>
-    <hyperlink ref="B19" r:id="rId10" location="'Plan'!A1" display="Plan"/>
+    <hyperlink ref="B14" r:id="rId5" location="'Organigramas'!A1" display="Organigramas"/>
+    <hyperlink ref="B15" r:id="rId6" location="'Empresas'!A1" display="Empresas"/>
+    <hyperlink ref="B16" r:id="rId7" location="'Políticas'!A1" display="Políticas"/>
+    <hyperlink ref="B17" r:id="rId8" location="'KPIs'!A1" display="KPIs"/>
+    <hyperlink ref="B18" r:id="rId9" location="'Reuniones'!A1" display="Reuniones"/>
+    <hyperlink ref="B19" r:id="rId10" location="'Decisiones'!A1" display="Decisiones"/>
+    <hyperlink ref="B20" r:id="rId11" location="'Plan'!A1" display="Plan"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2431,6 +2615,226 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF98C9EB"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="G4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="G5" s="13"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="G6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>496</v>
+      </c>
+      <c r="G8" s="13"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>497</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="G9" s="13"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF98C9EB"/>
@@ -2450,138 +2854,138 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>469</v>
+        <v>502</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>470</v>
+        <v>503</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>471</v>
+        <v>504</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>472</v>
+        <v>505</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>473</v>
+        <v>506</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>474</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>475</v>
+        <v>508</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>477</v>
+        <v>510</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>478</v>
+        <v>511</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="G2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>480</v>
+        <v>513</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>481</v>
+        <v>514</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>482</v>
+        <v>515</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="G3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>483</v>
+        <v>516</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>484</v>
+        <v>517</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>485</v>
+        <v>518</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13" t="s">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>486</v>
+        <v>519</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>487</v>
+        <v>520</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>488</v>
+        <v>521</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>489</v>
+        <v>522</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13" t="s">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="G5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>490</v>
+        <v>523</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>491</v>
+        <v>524</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>492</v>
+        <v>525</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13" t="s">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="G6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>493</v>
+        <v>526</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>494</v>
+        <v>527</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>495</v>
+        <v>528</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13" t="s">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="G7" s="13"/>
     </row>
@@ -2596,7 +3000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF98C9EB"/>
@@ -2616,129 +3020,129 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>496</v>
+        <v>529</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>497</v>
+        <v>530</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>498</v>
+        <v>531</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>499</v>
+        <v>532</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>500</v>
+        <v>533</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>501</v>
+        <v>534</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>502</v>
+        <v>535</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>503</v>
+        <v>536</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>504</v>
+        <v>537</v>
       </c>
       <c r="G2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>505</v>
+        <v>538</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>506</v>
+        <v>539</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>507</v>
+        <v>540</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>508</v>
+        <v>541</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>504</v>
+        <v>537</v>
       </c>
       <c r="G3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>509</v>
+        <v>542</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>510</v>
+        <v>543</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>511</v>
+        <v>544</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>512</v>
+        <v>545</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>504</v>
+        <v>537</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>513</v>
+        <v>546</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>514</v>
+        <v>547</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>515</v>
+        <v>548</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>516</v>
+        <v>549</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>504</v>
+        <v>537</v>
       </c>
       <c r="G5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>517</v>
+        <v>550</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>518</v>
+        <v>551</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>519</v>
+        <v>552</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>520</v>
+        <v>553</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>504</v>
+        <v>537</v>
       </c>
       <c r="G6" s="13"/>
     </row>
@@ -2773,1037 +3177,1037 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C3" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>70</v>
-      </c>
       <c r="F5" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D9" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>91</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D14" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>111</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -3834,25 +4238,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D2" s="15" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E2" s="15"/>
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
       <c r="I2" s="15" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
       <c r="M2" s="15" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
@@ -3862,92 +4266,92 @@
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
       <c r="H4" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J4" s="17"/>
       <c r="K4" s="17"/>
       <c r="L4" s="17"/>
       <c r="M4" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
@@ -3961,42 +4365,42 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H5" s="17"/>
       <c r="I5" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17"/>
@@ -4009,41 +4413,41 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
       <c r="M6" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
       <c r="Q6" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R6" s="17"/>
       <c r="S6" s="18" t="str">
@@ -4053,37 +4457,37 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
       <c r="I7" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
@@ -4097,37 +4501,37 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
       <c r="H8" s="17"/>
       <c r="I8" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
@@ -4141,33 +4545,33 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
       <c r="H9" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
       <c r="M9" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
@@ -4181,32 +4585,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J10" s="17"/>
       <c r="K10" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
@@ -4221,38 +4625,38 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K11" s="17"/>
       <c r="L11" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M11" s="17"/>
       <c r="N11" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
@@ -4265,33 +4669,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
       <c r="F12" s="9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="17"/>
       <c r="I12" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J12" s="17"/>
       <c r="K12" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
       <c r="O12" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P12" s="17"/>
       <c r="Q12" s="17"/>
@@ -4303,40 +4707,40 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G13" s="17"/>
       <c r="H13" s="17"/>
       <c r="I13" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
       <c r="O13" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P13" s="17"/>
       <c r="Q13" s="17"/>
       <c r="R13" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S13" s="18" t="str">
         <f aca="false">IF(COUNTIF(D13:R13,"A")+COUNTIF(D13:R13,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D13:R13,"R")+COUNTIF(D13:R13,"A/R")=0,"Falta R","OK"))</f>
@@ -4345,27 +4749,27 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
       <c r="I14" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
@@ -4383,36 +4787,36 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M15" s="17"/>
       <c r="N15" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O15" s="17"/>
       <c r="P15" s="17"/>
@@ -4425,34 +4829,34 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O16" s="17"/>
       <c r="P16" s="17"/>
@@ -4465,32 +4869,32 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
@@ -4503,34 +4907,34 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O18" s="17"/>
       <c r="P18" s="17"/>
@@ -4543,13 +4947,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
@@ -4557,18 +4961,18 @@
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
       <c r="I19" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O19" s="17"/>
       <c r="P19" s="17"/>
@@ -4581,13 +4985,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
@@ -4595,20 +4999,20 @@
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
       <c r="I20" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O20" s="17"/>
       <c r="P20" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q20" s="17"/>
       <c r="R20" s="17"/>
@@ -4619,13 +5023,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
@@ -4633,20 +5037,20 @@
       <c r="G21" s="17"/>
       <c r="H21" s="17"/>
       <c r="I21" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O21" s="17"/>
       <c r="P21" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q21" s="17"/>
       <c r="R21" s="17"/>
@@ -4657,36 +5061,36 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L22" s="17"/>
       <c r="M22" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O22" s="17"/>
       <c r="P22" s="17"/>
@@ -4699,37 +5103,37 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
       <c r="I23" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J23" s="17"/>
       <c r="K23" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M23" s="17"/>
       <c r="N23" s="17"/>
       <c r="O23" s="17"/>
       <c r="P23" s="17"/>
       <c r="Q23" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="R23" s="17"/>
       <c r="S23" s="18" t="str">
@@ -4739,13 +5143,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
@@ -4753,20 +5157,20 @@
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
       <c r="I24" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M24" s="17"/>
       <c r="N24" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O24" s="17"/>
       <c r="P24" s="17"/>
@@ -4779,13 +5183,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
@@ -4793,19 +5197,19 @@
       <c r="G25" s="17"/>
       <c r="H25" s="17"/>
       <c r="I25" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J25" s="17"/>
       <c r="K25" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
       <c r="O25" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P25" s="17"/>
       <c r="Q25" s="17"/>
@@ -4817,35 +5221,35 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
       <c r="G26" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H26" s="17"/>
       <c r="I26" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M26" s="17"/>
       <c r="N26" s="17"/>
       <c r="O26" s="17"/>
       <c r="P26" s="17"/>
       <c r="Q26" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R26" s="17"/>
       <c r="S26" s="18" t="str">
@@ -4855,35 +5259,35 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J27" s="17"/>
       <c r="K27" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L27" s="17"/>
       <c r="M27" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N27" s="17"/>
       <c r="O27" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P27" s="17"/>
       <c r="Q27" s="17"/>
@@ -4895,36 +5299,36 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
       <c r="G28" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J28" s="17"/>
       <c r="K28" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L28" s="17"/>
       <c r="M28" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O28" s="17"/>
       <c r="P28" s="17"/>
@@ -4937,13 +5341,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
@@ -4951,20 +5355,20 @@
       <c r="G29" s="17"/>
       <c r="H29" s="17"/>
       <c r="I29" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J29" s="17"/>
       <c r="K29" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" s="17"/>
       <c r="O29" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P29" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q29" s="17"/>
       <c r="R29" s="17"/>
@@ -4975,13 +5379,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
@@ -4989,25 +5393,25 @@
       <c r="G30" s="17"/>
       <c r="H30" s="17"/>
       <c r="I30" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P30" s="17"/>
       <c r="Q30" s="17"/>
@@ -5019,13 +5423,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -5033,19 +5437,19 @@
       <c r="G31" s="17"/>
       <c r="H31" s="17"/>
       <c r="I31" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" s="17"/>
       <c r="O31" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P31" s="17"/>
       <c r="Q31" s="17"/>
@@ -5057,13 +5461,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
@@ -5071,19 +5475,19 @@
       <c r="G32" s="17"/>
       <c r="H32" s="17"/>
       <c r="I32" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" s="17"/>
       <c r="O32" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P32" s="17"/>
       <c r="Q32" s="17"/>
@@ -5095,13 +5499,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
@@ -5109,26 +5513,26 @@
       <c r="G33" s="17"/>
       <c r="H33" s="17"/>
       <c r="I33" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O33" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P33" s="17"/>
       <c r="Q33" s="17"/>
       <c r="R33" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S33" s="18" t="str">
         <f aca="false">IF(COUNTIF(D33:R33,"A")+COUNTIF(D33:R33,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D33:R33,"R")+COUNTIF(D33:R33,"A/R")=0,"Falta R","OK"))</f>
@@ -5137,13 +5541,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
@@ -5151,22 +5555,22 @@
       <c r="G34" s="17"/>
       <c r="H34" s="17"/>
       <c r="I34" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J34" s="17"/>
       <c r="K34" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
       <c r="O34" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P34" s="17"/>
       <c r="Q34" s="17"/>
       <c r="R34" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S34" s="18" t="str">
         <f aca="false">IF(COUNTIF(D34:R34,"A")+COUNTIF(D34:R34,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D34:R34,"R")+COUNTIF(D34:R34,"A/R")=0,"Falta R","OK"))</f>
@@ -5175,13 +5579,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
@@ -5189,18 +5593,18 @@
       <c r="G35" s="17"/>
       <c r="H35" s="17"/>
       <c r="I35" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O35" s="17"/>
       <c r="P35" s="17"/>
@@ -5213,13 +5617,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
@@ -5227,20 +5631,20 @@
       <c r="G36" s="17"/>
       <c r="H36" s="17"/>
       <c r="I36" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K36" s="17"/>
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O36" s="17"/>
       <c r="P36" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q36" s="17"/>
       <c r="R36" s="17"/>
@@ -5251,13 +5655,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D37" s="17"/>
       <c r="E37" s="17"/>
@@ -5265,20 +5669,20 @@
       <c r="G37" s="17"/>
       <c r="H37" s="17"/>
       <c r="I37" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L37" s="17"/>
       <c r="M37" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O37" s="17"/>
       <c r="P37" s="17"/>
@@ -5291,13 +5695,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
@@ -5305,20 +5709,20 @@
       <c r="G38" s="17"/>
       <c r="H38" s="17"/>
       <c r="I38" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K38" s="17"/>
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O38" s="17"/>
       <c r="P38" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q38" s="17"/>
       <c r="R38" s="17"/>
@@ -5329,35 +5733,35 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D39" s="17"/>
       <c r="E39" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
       <c r="H39" s="17"/>
       <c r="I39" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J39" s="17"/>
       <c r="K39" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L39" s="17"/>
       <c r="M39" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N39" s="17"/>
       <c r="O39" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P39" s="17"/>
       <c r="Q39" s="17"/>
@@ -5369,35 +5773,35 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D40" s="17"/>
       <c r="E40" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
       <c r="H40" s="17"/>
       <c r="I40" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J40" s="17"/>
       <c r="K40" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L40" s="17"/>
       <c r="M40" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N40" s="17"/>
       <c r="O40" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P40" s="17"/>
       <c r="Q40" s="17"/>
@@ -5409,35 +5813,35 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D41" s="17"/>
       <c r="E41" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G41" s="17"/>
       <c r="H41" s="17"/>
       <c r="I41" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
       <c r="L41" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M41" s="17"/>
       <c r="N41" s="17"/>
       <c r="O41" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P41" s="17"/>
       <c r="Q41" s="17"/>
@@ -5449,37 +5853,37 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D42" s="17"/>
       <c r="E42" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F42" s="17"/>
       <c r="G42" s="17"/>
       <c r="H42" s="17"/>
       <c r="I42" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L42" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M42" s="17"/>
       <c r="N42" s="17"/>
       <c r="O42" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P42" s="17"/>
       <c r="Q42" s="17"/>
@@ -5491,37 +5895,37 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D43" s="17"/>
       <c r="E43" s="17"/>
       <c r="F43" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H43" s="17"/>
       <c r="I43" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J43" s="17"/>
       <c r="K43" s="17"/>
       <c r="L43" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M43" s="17"/>
       <c r="N43" s="17"/>
       <c r="O43" s="17"/>
       <c r="P43" s="17"/>
       <c r="Q43" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="R43" s="17"/>
       <c r="S43" s="18" t="str">
@@ -5531,37 +5935,37 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D44" s="17"/>
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
       <c r="G44" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J44" s="17"/>
       <c r="K44" s="17"/>
       <c r="L44" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M44" s="17"/>
       <c r="N44" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O44" s="17"/>
       <c r="P44" s="17"/>
       <c r="Q44" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R44" s="17"/>
       <c r="S44" s="18" t="str">
@@ -5571,30 +5975,30 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D45" s="17"/>
       <c r="E45" s="17"/>
       <c r="F45" s="17"/>
       <c r="G45" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H45" s="17"/>
       <c r="I45" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J45" s="17"/>
       <c r="K45" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L45" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M45" s="17"/>
       <c r="N45" s="17"/>
@@ -5609,37 +6013,37 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="17"/>
       <c r="G46" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H46" s="17"/>
       <c r="I46" s="17"/>
       <c r="J46" s="17"/>
       <c r="K46" s="17"/>
       <c r="L46" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M46" s="17"/>
       <c r="N46" s="17"/>
       <c r="O46" s="17"/>
       <c r="P46" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q46" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R46" s="17"/>
       <c r="S46" s="18" t="str">
@@ -5649,37 +6053,37 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
       <c r="F47" s="17"/>
       <c r="G47" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H47" s="17"/>
       <c r="I47" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J47" s="17"/>
       <c r="K47" s="17"/>
       <c r="L47" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M47" s="17"/>
       <c r="N47" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O47" s="17"/>
       <c r="P47" s="17"/>
       <c r="Q47" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R47" s="17"/>
       <c r="S47" s="18" t="str">
@@ -5689,7 +6093,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -5734,370 +6138,370 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -6131,36 +6535,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -6171,10 +6575,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -6185,10 +6589,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
@@ -6199,10 +6603,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
@@ -6213,10 +6617,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
@@ -6227,10 +6631,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -6241,10 +6645,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="20"/>
@@ -6255,10 +6659,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -6269,10 +6673,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
@@ -6283,10 +6687,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
@@ -6297,10 +6701,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
@@ -6311,10 +6715,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
@@ -6325,10 +6729,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -6339,10 +6743,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
@@ -6353,10 +6757,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
@@ -6367,10 +6771,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
@@ -6381,10 +6785,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -6395,10 +6799,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="20"/>
@@ -6409,10 +6813,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="20"/>
@@ -6423,10 +6827,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="20"/>
@@ -6437,10 +6841,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="20"/>
@@ -6451,10 +6855,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20"/>
@@ -6465,10 +6869,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
@@ -6479,10 +6883,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="20"/>
@@ -6493,10 +6897,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
@@ -6507,10 +6911,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
@@ -6521,10 +6925,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="20"/>
@@ -6535,10 +6939,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="20"/>
@@ -6549,10 +6953,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
@@ -6563,7 +6967,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -6578,6 +6982,1421 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF98C9EB"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:L45"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C3" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C4" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C5" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C17" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C18" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C19" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C20" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C26" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C30" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C31" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C32" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C36" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C37" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G37" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C38" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G38" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C41" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G41" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J41" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C42" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G42" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C43" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="E43" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G43" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J43" s="22"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C44" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="E44" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="G44" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="13"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L45"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF98C9EB"/>
@@ -6599,177 +8418,177 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>324</v>
+        <v>357</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>325</v>
+        <v>358</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>326</v>
+        <v>359</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>328</v>
+        <v>361</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>330</v>
+        <v>363</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>331</v>
+        <v>364</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="H2" s="13" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="I2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>335</v>
+        <v>368</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>336</v>
+        <v>369</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
       <c r="H3" s="13" t="s">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="I3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13" t="s">
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="I4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
       <c r="H5" s="13" t="s">
-        <v>341</v>
+        <v>374</v>
       </c>
       <c r="I5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13" t="s">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="I6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13" t="s">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="I7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="I8" s="13"/>
     </row>
@@ -6784,7 +8603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF98C9EB"/>
@@ -6802,197 +8621,197 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>350</v>
+        <v>383</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>351</v>
+        <v>384</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>352</v>
+        <v>385</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>357</v>
+        <v>390</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="F2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="F3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>364</v>
+        <v>397</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="F4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>365</v>
+        <v>398</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>367</v>
+        <v>400</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="F5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>368</v>
+        <v>401</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="F6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>372</v>
+        <v>405</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="F7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="F8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>378</v>
+        <v>411</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="F9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>379</v>
+        <v>412</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>380</v>
+        <v>413</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="F10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>382</v>
+        <v>415</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>383</v>
+        <v>416</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="F11" s="13"/>
     </row>
@@ -7007,7 +8826,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF98C9EB"/>
@@ -7027,474 +8846,254 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>385</v>
+        <v>418</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>353</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>391</v>
+        <v>424</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>392</v>
+        <v>425</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>393</v>
+        <v>426</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>394</v>
+        <v>427</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>396</v>
+        <v>429</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>398</v>
+        <v>431</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>399</v>
+        <v>432</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>401</v>
+        <v>434</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>402</v>
+        <v>435</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>404</v>
+        <v>437</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>408</v>
+        <v>441</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>409</v>
+        <v>442</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>410</v>
+        <v>443</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>411</v>
+        <v>444</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>412</v>
+        <v>445</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>413</v>
+        <v>446</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>414</v>
+        <v>447</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>415</v>
+        <v>448</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>417</v>
+        <v>450</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>419</v>
+        <v>452</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>420</v>
+        <v>453</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>422</v>
+        <v>455</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>423</v>
+        <v>456</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>424</v>
+        <v>457</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF98C9EB"/>
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>432</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>434</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>438</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>440</v>
-      </c>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="G4" s="13"/>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>447</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>449</v>
-      </c>
-      <c r="G5" s="13"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>451</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>452</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>454</v>
-      </c>
-      <c r="G6" s="13"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>459</v>
-      </c>
-      <c r="G7" s="13"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>460</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>461</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>462</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="G8" s="13"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>464</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>466</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>468</v>
-      </c>
-      <c r="G9" s="13"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/modelo_planificacion/Kit_Modelo_Planificacion_CL.xlsx
+++ b/modelo_planificacion/Kit_Modelo_Planificacion_CL.xlsx
@@ -22,7 +22,7 @@
     <sheet name="Plan" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Organigramas!$A$1:$L$45</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Organigramas!$A$1:$L$60</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="596">
   <si>
     <t xml:space="preserve">Modelo de planificación corporativo · CL Grupo Industrial</t>
   </si>
@@ -996,9 +996,66 @@
     <t xml:space="preserve">Corporativo · Planificación</t>
   </si>
   <si>
+    <t xml:space="preserve">Enrique Tejada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel Rodriguez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Leal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesus Amigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicente Hernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Trigo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ondupet</t>
   </si>
   <si>
+    <t xml:space="preserve">Victoriano Perez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbara Ayuste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel Castro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel Jesus Trinidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monica Gordillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jefes Turno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernando Tolosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antonio Nogales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ondupack Almendralejo</t>
   </si>
   <si>
@@ -1047,24 +1104,54 @@
     <t xml:space="preserve">% planificación</t>
   </si>
   <si>
+    <t xml:space="preserve">As-is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsable Planificacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Responsable Técnico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsable Planificacion · Enrique Tejada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Responsable Procesos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel Rodríguez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Programador .NET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsable Procesos · Manuel Rodríguez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicente Hernández</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Nuevo puesto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacante</t>
+  </si>
+  <si>
     <t xml:space="preserve">To-be</t>
   </si>
   <si>
     <t xml:space="preserve">Dirección General</t>
   </si>
   <si>
-    <t xml:space="preserve">Vacante</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dirección</t>
   </si>
   <si>
     <t xml:space="preserve">      Director/a de Planificación</t>
   </si>
   <si>
-    <t xml:space="preserve">Planificación</t>
-  </si>
-  <si>
     <t xml:space="preserve">            Responsable de procesos (Functional Lead)</t>
   </si>
   <si>
@@ -1087,6 +1174,45 @@
   </si>
   <si>
     <t xml:space="preserve">Uno por planta; ver el organigrama de cada empresa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director Planta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Responsable Planificación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director Planta · Manuel Castro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Responsable Comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Comercial / Logística Externa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsable Comercial · Manuel Jesus Trinidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Responsable Compras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Gestor Compras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsable Compras · Antonio Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Responsable Produccion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Manuel Barroso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Jefes Turno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsable Produccion · Juan Manuel Barroso</t>
   </si>
   <si>
     <t xml:space="preserve">Corporativo.</t>
@@ -2021,11 +2147,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2434,7 +2560,7 @@
       </c>
       <c r="D13" s="7" t="n">
         <f aca="false">COUNTA(Asignación!C:C)-1</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>20</v>
@@ -2449,7 +2575,7 @@
       </c>
       <c r="D14" s="7" t="n">
         <f aca="false">COUNTA(Organigramas!D:D)-1</f>
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>23</v>
@@ -2634,22 +2760,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>458</v>
+        <v>500</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>459</v>
+        <v>501</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>460</v>
+        <v>502</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>462</v>
+        <v>504</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>318</v>
@@ -2657,169 +2783,169 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>464</v>
+        <v>506</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>465</v>
+        <v>507</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>466</v>
+        <v>508</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>467</v>
+        <v>509</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>468</v>
+        <v>510</v>
       </c>
       <c r="G2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>469</v>
+        <v>511</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>470</v>
+        <v>512</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>471</v>
+        <v>513</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>472</v>
+        <v>514</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>473</v>
+        <v>515</v>
       </c>
       <c r="G3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>474</v>
+        <v>516</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>470</v>
+        <v>512</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>475</v>
+        <v>517</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>476</v>
+        <v>518</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>477</v>
+        <v>519</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>478</v>
+        <v>520</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>84</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>479</v>
+        <v>521</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>480</v>
+        <v>522</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>481</v>
+        <v>523</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>482</v>
+        <v>524</v>
       </c>
       <c r="G5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>483</v>
+        <v>525</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>90</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>484</v>
+        <v>526</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>485</v>
+        <v>527</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>486</v>
+        <v>528</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>487</v>
+        <v>529</v>
       </c>
       <c r="G6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>488</v>
+        <v>530</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>84</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>489</v>
+        <v>531</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>490</v>
+        <v>532</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>491</v>
+        <v>533</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>492</v>
+        <v>534</v>
       </c>
       <c r="G7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>493</v>
+        <v>535</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>470</v>
+        <v>512</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>494</v>
+        <v>536</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>495</v>
+        <v>537</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>496</v>
+        <v>538</v>
       </c>
       <c r="G8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>497</v>
+        <v>539</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>498</v>
+        <v>540</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>499</v>
+        <v>541</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>501</v>
+        <v>543</v>
       </c>
       <c r="G9" s="13"/>
     </row>
@@ -2854,138 +2980,138 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>502</v>
+        <v>544</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>503</v>
+        <v>545</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>504</v>
+        <v>546</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>505</v>
+        <v>547</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>506</v>
+        <v>548</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>387</v>
+        <v>429</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>507</v>
+        <v>549</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>508</v>
+        <v>550</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>509</v>
+        <v>551</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>510</v>
+        <v>552</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>511</v>
+        <v>553</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
-        <v>512</v>
+        <v>554</v>
       </c>
       <c r="G2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>513</v>
+        <v>555</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>514</v>
+        <v>556</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>515</v>
+        <v>557</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>226</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>512</v>
+        <v>554</v>
       </c>
       <c r="G3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>516</v>
+        <v>558</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>517</v>
+        <v>559</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>518</v>
+        <v>560</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>226</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13" t="s">
-        <v>512</v>
+        <v>554</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>519</v>
+        <v>561</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>520</v>
+        <v>562</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>521</v>
+        <v>563</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>522</v>
+        <v>564</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13" t="s">
-        <v>512</v>
+        <v>554</v>
       </c>
       <c r="G5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>523</v>
+        <v>565</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>524</v>
+        <v>566</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>525</v>
+        <v>567</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>226</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13" t="s">
-        <v>512</v>
+        <v>554</v>
       </c>
       <c r="G6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>526</v>
+        <v>568</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>527</v>
+        <v>569</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>528</v>
+        <v>570</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>226</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13" t="s">
-        <v>512</v>
+        <v>554</v>
       </c>
       <c r="G7" s="13"/>
     </row>
@@ -3020,22 +3146,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>529</v>
+        <v>571</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>530</v>
+        <v>572</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>531</v>
+        <v>573</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>532</v>
+        <v>574</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>386</v>
+        <v>428</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>387</v>
+        <v>429</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>318</v>
@@ -3043,106 +3169,106 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>533</v>
+        <v>575</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>534</v>
+        <v>576</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>535</v>
+        <v>577</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>536</v>
+        <v>578</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>65</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>537</v>
+        <v>579</v>
       </c>
       <c r="G2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>538</v>
+        <v>580</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>539</v>
+        <v>581</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>540</v>
+        <v>582</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>541</v>
+        <v>583</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>64</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>537</v>
+        <v>579</v>
       </c>
       <c r="G3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>542</v>
+        <v>584</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>543</v>
+        <v>585</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>544</v>
+        <v>586</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>545</v>
+        <v>587</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>65</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>537</v>
+        <v>579</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>546</v>
+        <v>588</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>547</v>
+        <v>589</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>548</v>
+        <v>590</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>549</v>
+        <v>591</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>64</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>537</v>
+        <v>579</v>
       </c>
       <c r="G5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>550</v>
+        <v>592</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>551</v>
+        <v>593</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>552</v>
+        <v>594</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>553</v>
+        <v>595</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>64</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>537</v>
+        <v>579</v>
       </c>
       <c r="G6" s="13"/>
     </row>
@@ -6521,7 +6647,7 @@
     <tabColor rgb="FF98C9EB"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -6566,10 +6692,14 @@
       <c r="B2" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="20"/>
+      <c r="C2" s="13" t="s">
+        <v>320</v>
+      </c>
       <c r="D2" s="20"/>
       <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="F2" s="13" t="s">
+        <v>321</v>
+      </c>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
@@ -6580,10 +6710,14 @@
       <c r="B3" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="20"/>
+      <c r="C3" s="13" t="s">
+        <v>322</v>
+      </c>
       <c r="D3" s="20"/>
       <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
+      <c r="F3" s="13" t="s">
+        <v>321</v>
+      </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
@@ -6592,12 +6726,16 @@
         <v>319</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="20"/>
+        <v>264</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>323</v>
+      </c>
       <c r="D4" s="20"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="F4" s="13" t="s">
+        <v>321</v>
+      </c>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
     </row>
@@ -6606,12 +6744,16 @@
         <v>319</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="20"/>
+        <v>264</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>324</v>
+      </c>
       <c r="D5" s="20"/>
       <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="F5" s="13" t="s">
+        <v>321</v>
+      </c>
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
@@ -6622,229 +6764,293 @@
       <c r="B6" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="C6" s="20"/>
+      <c r="C6" s="13" t="s">
+        <v>325</v>
+      </c>
       <c r="D6" s="20"/>
       <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="F6" s="13" t="s">
+        <v>321</v>
+      </c>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="20"/>
+        <v>264</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>326</v>
+      </c>
       <c r="D7" s="20"/>
       <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="F7" s="13" t="s">
+        <v>321</v>
+      </c>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="20"/>
+        <v>102</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>328</v>
+      </c>
       <c r="D8" s="20"/>
       <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="F8" s="13" t="s">
+        <v>329</v>
+      </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="20"/>
+        <v>111</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>328</v>
+      </c>
       <c r="D9" s="20"/>
       <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="F9" s="13" t="s">
+        <v>329</v>
+      </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" s="20"/>
+        <v>103</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>328</v>
+      </c>
       <c r="D10" s="20"/>
       <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="F10" s="13" t="s">
+        <v>329</v>
+      </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="20"/>
+        <v>237</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>328</v>
+      </c>
       <c r="D11" s="20"/>
       <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="F11" s="13" t="s">
+        <v>330</v>
+      </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="20"/>
+        <v>237</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>331</v>
+      </c>
       <c r="D12" s="20"/>
       <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="F12" s="13" t="s">
+        <v>332</v>
+      </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="20"/>
+        <v>139</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>331</v>
+      </c>
       <c r="D13" s="20"/>
       <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="F13" s="13" t="s">
+        <v>332</v>
+      </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="20"/>
+        <v>197</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>333</v>
+      </c>
       <c r="D14" s="20"/>
       <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
+      <c r="F14" s="13" t="s">
+        <v>321</v>
+      </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="20"/>
+        <v>291</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>334</v>
+      </c>
       <c r="D15" s="20"/>
       <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="F15" s="13" t="s">
+        <v>321</v>
+      </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" s="20"/>
+        <v>291</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>335</v>
+      </c>
       <c r="D16" s="20"/>
       <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
+      <c r="F16" s="13" t="s">
+        <v>332</v>
+      </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="20"/>
+        <v>91</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>335</v>
+      </c>
       <c r="D17" s="20"/>
       <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
+      <c r="F17" s="13" t="s">
+        <v>336</v>
+      </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C18" s="20"/>
+        <v>128</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>335</v>
+      </c>
       <c r="D18" s="20"/>
       <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
+      <c r="F18" s="13" t="s">
+        <v>329</v>
+      </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="20"/>
+        <v>198</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>337</v>
+      </c>
       <c r="D19" s="20"/>
       <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
+      <c r="F19" s="13" t="s">
+        <v>321</v>
+      </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="20"/>
+        <v>74</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>338</v>
+      </c>
       <c r="D20" s="20"/>
       <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
+      <c r="F20" s="13" t="s">
+        <v>321</v>
+      </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" s="20"/>
+        <v>237</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>339</v>
+      </c>
       <c r="D21" s="20"/>
       <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+      <c r="F21" s="13" t="s">
+        <v>321</v>
+      </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="20"/>
@@ -6855,10 +7061,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20"/>
@@ -6869,10 +7075,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
@@ -6883,10 +7089,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="20"/>
@@ -6897,10 +7103,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
@@ -6911,10 +7117,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
@@ -6925,10 +7131,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="20"/>
@@ -6939,10 +7145,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="20"/>
@@ -6953,10 +7159,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
@@ -6965,9 +7171,163 @@
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
     </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+    </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
-        <v>326</v>
+      <c r="A32" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="19" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -6987,7 +7347,7 @@
     <tabColor rgb="FF98C9EB"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -7008,1383 +7368,1819 @@
         <v>312</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="L1" s="9" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="C2" s="13" t="n">
+      <c r="B2" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="C2" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>338</v>
+      <c r="D2" s="21" t="s">
+        <v>357</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
+        <v>320</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C3" s="22" t="n">
+      <c r="B3" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>341</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G3" s="22" t="s">
+      <c r="D3" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G10" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22" t="s">
-        <v>338</v>
-      </c>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="H10" s="21"/>
+      <c r="I10" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C4" s="22" t="n">
+      <c r="B11" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="22" t="s">
-        <v>343</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G4" s="22" t="s">
+      <c r="D11" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G11" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22" t="s">
+      <c r="H11" s="21"/>
+      <c r="I11" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C5" s="22" t="n">
+      <c r="B12" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C12" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="22" t="s">
-        <v>344</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G5" s="22" t="s">
+      <c r="D12" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G12" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22" t="s">
+      <c r="H12" s="21"/>
+      <c r="I12" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C6" s="22" t="n">
+      <c r="B13" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C13" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="22" t="s">
-        <v>345</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G6" s="22" t="s">
+      <c r="D13" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G13" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22" t="s">
+      <c r="H13" s="21"/>
+      <c r="I13" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C7" s="22" t="n">
+      <c r="B14" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C14" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G7" s="22" t="s">
+      <c r="D14" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G14" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22" t="s">
+      <c r="H14" s="21"/>
+      <c r="I14" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C8" s="22" t="n">
+      <c r="B15" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C15" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="22" t="s">
-        <v>347</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G8" s="22" t="s">
+      <c r="D15" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G15" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22" t="s">
-        <v>348</v>
-      </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
+      <c r="H15" s="21"/>
+      <c r="I15" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C9" s="22" t="n">
+      <c r="B16" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C16" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="22" t="s">
-        <v>349</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G9" s="22" t="s">
+      <c r="D16" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G16" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22" t="s">
+      <c r="H16" s="21"/>
+      <c r="I16" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="C10" s="13" t="n">
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="C17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C11" s="22" t="n">
+      <c r="D17" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G11" s="22" t="s">
+      <c r="D18" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G18" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C12" s="22" t="n">
+      <c r="H18" s="21"/>
+      <c r="I18" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="C20" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C14" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F17" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C18" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C19" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C20" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F20" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
+      <c r="D20" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="E21" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>339</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>340</v>
+        <v>237</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
+      <c r="I21" s="13" t="s">
+        <v>382</v>
+      </c>
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>339</v>
+        <v>387</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>331</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>340</v>
+        <v>237</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="I22" s="13"/>
+        <v>237</v>
+      </c>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13" t="s">
+        <v>388</v>
+      </c>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
-      <c r="L22" s="13" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="B23" s="22" t="s">
+      <c r="L22" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="F24" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C26" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F23" s="22" t="s">
+      <c r="D26" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="J26" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C27" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C28" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C29" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C32" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="J32" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C33" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C34" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C35" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C38" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G38" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="J38" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C39" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C40" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G40" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J40" s="21"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C41" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="21"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="B43" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C44" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="E44" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G44" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22" t="s">
+      <c r="H44" s="21"/>
+      <c r="I44" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J23" s="22" t="s">
+      <c r="J44" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C24" s="22" t="n">
+      <c r="K44" s="21"/>
+      <c r="L44" s="21" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C45" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F24" s="22" t="s">
+      <c r="D45" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J45" s="21"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="21"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="B46" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G46" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J46" s="21"/>
+      <c r="K46" s="21"/>
+      <c r="L46" s="21"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H47" s="21"/>
+      <c r="I47" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J47" s="21"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="21"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="13" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C50" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G50" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="H50" s="21"/>
+      <c r="I50" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="J50" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="K50" s="21"/>
+      <c r="L50" s="21" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C51" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G51" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22" t="s">
+      <c r="H51" s="21"/>
+      <c r="I51" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C25" s="22" t="n">
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C52" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G25" s="22" t="s">
+      <c r="D52" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G52" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22" t="s">
+      <c r="H52" s="21"/>
+      <c r="I52" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C26" s="22" t="n">
+      <c r="J52" s="21"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C53" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G26" s="22" t="s">
+      <c r="D53" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G53" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22" t="s">
+      <c r="H53" s="21"/>
+      <c r="I53" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="C27" s="13" t="n">
+      <c r="J53" s="21"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C54" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D54" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E27" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G27" s="13" t="s">
+      <c r="E54" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G54" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="C28" s="13" t="n">
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C55" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D55" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="E28" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G28" s="13" t="s">
+      <c r="E55" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F55" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G55" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="H55" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C29" s="22" t="n">
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C56" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G29" s="22" t="s">
+      <c r="D56" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="E56" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G56" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22" t="s">
+      <c r="H56" s="21"/>
+      <c r="I56" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J29" s="22" t="s">
+      <c r="J56" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C30" s="22" t="n">
+      <c r="K56" s="21"/>
+      <c r="L56" s="21" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C57" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F30" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G30" s="22" t="s">
+      <c r="D57" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G57" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22" t="s">
+      <c r="H57" s="21"/>
+      <c r="I57" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C31" s="22" t="n">
+      <c r="J57" s="21"/>
+      <c r="K57" s="21"/>
+      <c r="L57" s="21"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C58" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D31" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F31" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G31" s="22" t="s">
+      <c r="D58" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="E58" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G58" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22" t="s">
+      <c r="H58" s="21"/>
+      <c r="I58" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C32" s="22" t="n">
+      <c r="J58" s="21"/>
+      <c r="K58" s="21"/>
+      <c r="L58" s="21"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C59" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D32" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G32" s="22" t="s">
+      <c r="D59" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="E59" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G59" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22" t="s">
+      <c r="H59" s="21"/>
+      <c r="I59" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="C33" s="13" t="n">
+      <c r="J59" s="21"/>
+      <c r="K59" s="21"/>
+      <c r="L59" s="21"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C60" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D60" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E33" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G33" s="13" t="s">
+      <c r="E60" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G60" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="C34" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="22" t="s">
-        <v>324</v>
-      </c>
-      <c r="B35" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C35" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G35" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="J35" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="22" t="s">
-        <v>324</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C36" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="22" t="s">
-        <v>324</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C37" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F37" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G37" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="22" t="s">
-        <v>324</v>
-      </c>
-      <c r="B38" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C38" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F38" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G38" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="C39" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="C40" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E40" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G40" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H40" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
-      <c r="L40" s="13" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="22" t="s">
-        <v>325</v>
-      </c>
-      <c r="B41" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C41" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F41" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G41" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="J41" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="22" t="s">
-        <v>325</v>
-      </c>
-      <c r="B42" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C42" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F42" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G42" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J42" s="22"/>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="22" t="s">
-        <v>325</v>
-      </c>
-      <c r="B43" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C43" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F43" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G43" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J43" s="22"/>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="22" t="s">
-        <v>325</v>
-      </c>
-      <c r="B44" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C44" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F44" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G44" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="C45" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
-      <c r="L45" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L45"/>
+  <autoFilter ref="A1:L60"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8418,28 +9214,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>357</v>
+        <v>399</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>358</v>
+        <v>400</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>359</v>
+        <v>401</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>361</v>
+        <v>403</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>362</v>
+        <v>404</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>363</v>
+        <v>405</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>364</v>
+        <v>406</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>318</v>
@@ -8453,142 +9249,142 @@
         <v>247</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>366</v>
+        <v>408</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="H2" s="13" t="s">
-        <v>367</v>
+        <v>409</v>
       </c>
       <c r="I2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>368</v>
+        <v>410</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>369</v>
+        <v>411</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
       <c r="H3" s="13" t="s">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c r="I3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>371</v>
+        <v>413</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13" t="s">
-        <v>373</v>
+        <v>415</v>
       </c>
       <c r="I4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>371</v>
+        <v>413</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
       <c r="H5" s="13" t="s">
-        <v>374</v>
+        <v>416</v>
       </c>
       <c r="I5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>375</v>
+        <v>417</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>376</v>
+        <v>418</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13" t="s">
-        <v>377</v>
+        <v>419</v>
       </c>
       <c r="I6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>375</v>
+        <v>417</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>376</v>
+        <v>418</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13" t="s">
-        <v>378</v>
+        <v>420</v>
       </c>
       <c r="I7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>379</v>
+        <v>421</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>381</v>
+        <v>423</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>382</v>
+        <v>424</v>
       </c>
       <c r="I8" s="13"/>
     </row>
@@ -8621,19 +9417,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>386</v>
+        <v>428</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>387</v>
+        <v>429</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>318</v>
@@ -8641,177 +9437,177 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>389</v>
+        <v>431</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>390</v>
+        <v>432</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>91</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>391</v>
+        <v>433</v>
       </c>
       <c r="F2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>392</v>
+        <v>434</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>393</v>
+        <v>435</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>394</v>
+        <v>436</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>65</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>391</v>
+        <v>433</v>
       </c>
       <c r="F3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>395</v>
+        <v>437</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>396</v>
+        <v>438</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>397</v>
+        <v>439</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>74</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>391</v>
+        <v>433</v>
       </c>
       <c r="F4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>398</v>
+        <v>440</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>399</v>
+        <v>441</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>400</v>
+        <v>442</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>64</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>391</v>
+        <v>433</v>
       </c>
       <c r="F5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>401</v>
+        <v>443</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>402</v>
+        <v>444</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13" t="s">
         <v>64</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>391</v>
+        <v>433</v>
       </c>
       <c r="F6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>403</v>
+        <v>445</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>404</v>
+        <v>446</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>405</v>
+        <v>447</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>74</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>391</v>
+        <v>433</v>
       </c>
       <c r="F7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>406</v>
+        <v>448</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>407</v>
+        <v>449</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>408</v>
+        <v>450</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>65</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>391</v>
+        <v>433</v>
       </c>
       <c r="F8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>409</v>
+        <v>451</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>411</v>
+        <v>453</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>64</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>391</v>
+        <v>433</v>
       </c>
       <c r="F9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>412</v>
+        <v>454</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>413</v>
+        <v>455</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>414</v>
+        <v>456</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>65</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>391</v>
+        <v>433</v>
       </c>
       <c r="F10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>415</v>
+        <v>457</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>416</v>
+        <v>458</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13" t="s">
         <v>91</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>391</v>
+        <v>433</v>
       </c>
       <c r="F11" s="13"/>
     </row>
@@ -8846,22 +9642,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>417</v>
+        <v>459</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>418</v>
+        <v>460</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>419</v>
+        <v>461</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>386</v>
+        <v>428</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>421</v>
+        <v>463</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>318</v>
@@ -8869,13 +9665,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>422</v>
+        <v>464</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>423</v>
+        <v>465</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>424</v>
+        <v>466</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>73</v>
@@ -8888,13 +9684,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>425</v>
+        <v>467</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>426</v>
+        <v>468</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>427</v>
+        <v>469</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>84</v>
@@ -8907,13 +9703,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>428</v>
+        <v>470</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>429</v>
+        <v>471</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>430</v>
+        <v>472</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>84</v>
@@ -8926,13 +9722,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>431</v>
+        <v>473</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>432</v>
+        <v>474</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>433</v>
+        <v>475</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>73</v>
@@ -8945,13 +9741,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>434</v>
+        <v>476</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>435</v>
+        <v>477</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>436</v>
+        <v>478</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>84</v>
@@ -8964,13 +9760,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>437</v>
+        <v>479</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>438</v>
+        <v>480</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>439</v>
+        <v>481</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>84</v>
@@ -8983,13 +9779,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>440</v>
+        <v>482</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>441</v>
+        <v>483</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>442</v>
+        <v>484</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>84</v>
@@ -9002,13 +9798,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>443</v>
+        <v>485</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>444</v>
+        <v>486</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>445</v>
+        <v>487</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>84</v>
@@ -9021,13 +9817,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>446</v>
+        <v>488</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>447</v>
+        <v>489</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>448</v>
+        <v>490</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>73</v>
@@ -9040,13 +9836,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>449</v>
+        <v>491</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>450</v>
+        <v>492</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>451</v>
+        <v>493</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>84</v>
@@ -9059,13 +9855,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>452</v>
+        <v>494</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>453</v>
+        <v>495</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>454</v>
+        <v>496</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>73</v>
@@ -9078,13 +9874,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>456</v>
+        <v>498</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>457</v>
+        <v>499</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>69</v>

--- a/modelo_planificacion/Kit_Modelo_Planificacion_CL.xlsx
+++ b/modelo_planificacion/Kit_Modelo_Planificacion_CL.xlsx
@@ -22,7 +22,7 @@
     <sheet name="Plan" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Organigramas!$A$1:$L$60</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Organigramas!$A$1:$L$61</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="601">
   <si>
     <t xml:space="preserve">Modelo de planificación corporativo · CL Grupo Industrial</t>
   </si>
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Origen de los datos</t>
   </si>
   <si>
-    <t xml:space="preserve">Propuesta inicial</t>
+    <t xml:space="preserve">Datos del equipo · export de la herramienta · 2026-10-07</t>
   </si>
   <si>
     <t xml:space="preserve">Generado</t>
@@ -735,15 +735,15 @@
     <t xml:space="preserve">Materiales</t>
   </si>
   <si>
+    <t xml:space="preserve">Producción</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dir. planta</t>
   </si>
   <si>
     <t xml:space="preserve">Comercial</t>
   </si>
   <si>
-    <t xml:space="preserve">Producción</t>
-  </si>
-  <si>
     <t xml:space="preserve">Logística</t>
   </si>
   <si>
@@ -894,6 +894,18 @@
     <t xml:space="preserve">Cobertura de stock · Roturas · % integración intercompany.</t>
   </si>
   <si>
+    <t xml:space="preserve">Responsable Producción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ejecuta el plan en máquina e informa de lo real.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumplir la secuencia · Registrar producción, paradas y consumos · Avisar de incidencias.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajustes operativos dentro del turno</t>
+  </si>
+  <si>
     <t xml:space="preserve">Otras áreas</t>
   </si>
   <si>
@@ -924,12 +936,6 @@
     <t xml:space="preserve">Servicio al cliente.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ejecuta el plan en máquina e informa de lo real.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumplir la secuencia · Registrar producción, paradas y consumos · Avisar de incidencias.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ajustes operativos dentro del turno.</t>
   </si>
   <si>
@@ -1008,126 +1014,132 @@
     <t xml:space="preserve">Daniel Leal</t>
   </si>
   <si>
+    <t xml:space="preserve">Jesus Amigo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondupet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernando Tolosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel Castro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoriano Perez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondupack Almendralejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondupack Navalmoral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antonio Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbara Ayuste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel Jesus Trinidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicente Hernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Trigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monica Gordillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Manuel Barroso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jefes Turno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En amarillo, los huecos por asignar (titular o suplente).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nivel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puesto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Persona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Área</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rol del modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De otra empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depende de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dependencia funcional de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% planificación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As-is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsable Planificacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Responsable Técnico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsable Planificacion · Enrique Tejada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Responsable Procesos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel Rodríguez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Programador .NET</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jesus Amigo</t>
   </si>
   <si>
-    <t xml:space="preserve">Vicente Hernandez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Trigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ondupet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoriano Perez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbara Ayuste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manuel Castro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manuel Jesus Trinidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monica Gordillo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jefes Turno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fernando Tolosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antonio Nogales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ondupack Almendralejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ondupack Navalmoral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papresa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En amarillo, los huecos por asignar (titular o suplente).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nivel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Persona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Área</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rol del modelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">De otra empresa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depende de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dependencia funcional de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% planificación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As-is</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsable Planificacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planificación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Responsable Técnico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsable Planificacion · Enrique Tejada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Responsable Procesos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manuel Rodríguez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Programador .NET</t>
-  </si>
-  <si>
     <t xml:space="preserve">Responsable Procesos · Manuel Rodríguez</t>
   </si>
   <si>
@@ -1176,40 +1188,43 @@
     <t xml:space="preserve">Uno por planta; ver el organigrama de cada empresa.</t>
   </si>
   <si>
-    <t xml:space="preserve">Director Planta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Responsable Planificación</t>
+    <t xml:space="preserve">Responsable Division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Director Planta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsable Division · Fernando Tolosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            Responsable Planificación</t>
   </si>
   <si>
     <t xml:space="preserve">Director Planta · Manuel Castro</t>
   </si>
   <si>
-    <t xml:space="preserve">      Responsable Comercial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Comercial / Logística Externa</t>
+    <t xml:space="preserve">            Responsable Comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  Comercial / Logística Externa</t>
   </si>
   <si>
     <t xml:space="preserve">Responsable Comercial · Manuel Jesus Trinidad</t>
   </si>
   <si>
-    <t xml:space="preserve">      Responsable Compras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Gestor Compras</t>
+    <t xml:space="preserve">            Responsable Compras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  Gestor Compras</t>
   </si>
   <si>
     <t xml:space="preserve">Responsable Compras · Antonio Nogales</t>
   </si>
   <si>
-    <t xml:space="preserve">      Responsable Produccion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Manuel Barroso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Jefes Turno</t>
+    <t xml:space="preserve">            Responsable Produccion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  Jefes Turno</t>
   </si>
   <si>
     <t xml:space="preserve">Responsable Produccion · Juan Manuel Barroso</t>
@@ -1260,7 +1275,7 @@
     <t xml:space="preserve">SAP</t>
   </si>
   <si>
-    <t xml:space="preserve">SAP · GIO · SIGPA</t>
+    <t xml:space="preserve">SAP · GIO · SIGPA </t>
   </si>
   <si>
     <t xml:space="preserve">Define el modelo y gobierna la planificación de todas las plantas.</t>
@@ -1278,7 +1293,7 @@
     <t xml:space="preserve">Cartón ondulado · onduladora y converting</t>
   </si>
   <si>
-    <t xml:space="preserve">Aplicación de escritorio (migración a web propuesta para 2027)</t>
+    <t xml:space="preserve">GIO Aplicación de escritorio (migración a web propuesta para 2027)</t>
   </si>
   <si>
     <t xml:space="preserve">Combiplan para combinar pedidos; consume papel intercompany.</t>
@@ -2529,7 +2544,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="7" t="n">
-        <f aca="false">COUNTIF(RACI!S:S,"OK")</f>
+        <f aca="false">COUNTIF(RACI!T:T,"OK")</f>
         <v>44</v>
       </c>
       <c r="E11" s="8" t="s">
@@ -2545,7 +2560,7 @@
       </c>
       <c r="D12" s="7" t="n">
         <f aca="false">COUNTA(Roles!A:A)-1</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>17</v>
@@ -2560,7 +2575,7 @@
       </c>
       <c r="D13" s="7" t="n">
         <f aca="false">COUNTA(Asignación!C:C)-1</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>20</v>
@@ -2575,7 +2590,7 @@
       </c>
       <c r="D14" s="7" t="n">
         <f aca="false">COUNTA(Organigramas!D:D)-1</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>23</v>
@@ -2760,192 +2775,192 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="G2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="G3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>84</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="G5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>90</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="G6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>84</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="G7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="G8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="G9" s="13"/>
     </row>
@@ -2980,138 +2995,138 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="G2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>226</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="G3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>226</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="G5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>226</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="G6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>226</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="G7" s="13"/>
     </row>
@@ -3146,129 +3161,129 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>65</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="G2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>64</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="G3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>65</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>64</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="G5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>64</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="G6" s="13"/>
     </row>
@@ -4353,13 +4368,13 @@
     <tabColor rgb="FF00263A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="4" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4381,14 +4396,15 @@
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="15"/>
+      <c r="N2" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="N2" s="15"/>
       <c r="O2" s="15"/>
       <c r="P2" s="15"/>
       <c r="Q2" s="15"/>
       <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
@@ -4437,15 +4453,18 @@
         <v>235</v>
       </c>
       <c r="P3" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4476,16 +4495,17 @@
       <c r="J4" s="17"/>
       <c r="K4" s="17"/>
       <c r="L4" s="17"/>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="17"/>
+      <c r="N4" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="N4" s="17"/>
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
-      <c r="S4" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D4:R4,"A")+COUNTIF(D4:R4,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D4:R4,"R")+COUNTIF(D4:R4,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D4:S4,"A")+COUNTIF(D4:S4,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D4:S4,"R")+COUNTIF(D4:S4,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -4522,18 +4542,19 @@
       <c r="L5" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M5" s="17"/>
       <c r="N5" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="O5" s="17"/>
+      <c r="O5" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
-      <c r="S5" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D5:R5,"A")+COUNTIF(D5:R5,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D5:R5,"R")+COUNTIF(D5:R5,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S5" s="17"/>
+      <c r="T5" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D5:S5,"A")+COUNTIF(D5:S5,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D5:S5,"R")+COUNTIF(D5:S5,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -4564,20 +4585,21 @@
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
-      <c r="M6" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="M6" s="17"/>
       <c r="N6" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="O6" s="17"/>
+      <c r="O6" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="P6" s="17"/>
-      <c r="Q6" s="11" t="s">
+      <c r="Q6" s="17"/>
+      <c r="R6" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="R6" s="17"/>
-      <c r="S6" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D6:R6,"A")+COUNTIF(D6:R6,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D6:R6,"R")+COUNTIF(D6:R6,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S6" s="17"/>
+      <c r="T6" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D6:S6,"A")+COUNTIF(D6:S6,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D6:S6,"R")+COUNTIF(D6:S6,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -4612,16 +4634,17 @@
       <c r="L7" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="17"/>
+      <c r="N7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N7" s="17"/>
       <c r="O7" s="17"/>
       <c r="P7" s="17"/>
       <c r="Q7" s="17"/>
       <c r="R7" s="17"/>
-      <c r="S7" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D7:R7,"A")+COUNTIF(D7:R7,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D7:R7,"R")+COUNTIF(D7:R7,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S7" s="17"/>
+      <c r="T7" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D7:S7,"A")+COUNTIF(D7:S7,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D7:S7,"R")+COUNTIF(D7:S7,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -4656,16 +4679,17 @@
       <c r="L8" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="17"/>
+      <c r="N8" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N8" s="17"/>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
       <c r="Q8" s="17"/>
       <c r="R8" s="17"/>
-      <c r="S8" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D8:R8,"A")+COUNTIF(D8:R8,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D8:R8,"R")+COUNTIF(D8:R8,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S8" s="17"/>
+      <c r="T8" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D8:S8,"A")+COUNTIF(D8:S8,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D8:S8,"R")+COUNTIF(D8:S8,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -4696,16 +4720,17 @@
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="17"/>
+      <c r="N9" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="N9" s="17"/>
       <c r="O9" s="17"/>
       <c r="P9" s="17"/>
       <c r="Q9" s="17"/>
       <c r="R9" s="17"/>
-      <c r="S9" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D9:R9,"A")+COUNTIF(D9:R9,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D9:R9,"R")+COUNTIF(D9:R9,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S9" s="17"/>
+      <c r="T9" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D9:S9,"A")+COUNTIF(D9:S9,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D9:S9,"R")+COUNTIF(D9:S9,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -4744,8 +4769,9 @@
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
       <c r="R10" s="17"/>
-      <c r="S10" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D10:R10,"A")+COUNTIF(D10:R10,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D10:R10,"R")+COUNTIF(D10:R10,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S10" s="17"/>
+      <c r="T10" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D10:S10,"A")+COUNTIF(D10:S10,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D10:S10,"R")+COUNTIF(D10:S10,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -4781,15 +4807,16 @@
         <v>50</v>
       </c>
       <c r="M11" s="17"/>
-      <c r="N11" s="11" t="s">
+      <c r="N11" s="17"/>
+      <c r="O11" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="O11" s="17"/>
       <c r="P11" s="17"/>
       <c r="Q11" s="17"/>
       <c r="R11" s="17"/>
-      <c r="S11" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D11:R11,"A")+COUNTIF(D11:R11,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D11:R11,"R")+COUNTIF(D11:R11,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S11" s="17"/>
+      <c r="T11" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D11:S11,"A")+COUNTIF(D11:S11,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D11:S11,"R")+COUNTIF(D11:S11,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -4820,14 +4847,15 @@
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="17"/>
+      <c r="P12" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="P12" s="17"/>
       <c r="Q12" s="17"/>
       <c r="R12" s="17"/>
-      <c r="S12" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D12:R12,"A")+COUNTIF(D12:R12,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D12:R12,"R")+COUNTIF(D12:R12,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S12" s="17"/>
+      <c r="T12" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D12:S12,"A")+COUNTIF(D12:S12,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D12:S12,"R")+COUNTIF(D12:S12,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -4860,16 +4888,17 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="17"/>
+      <c r="P13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="17"/>
       <c r="Q13" s="17"/>
-      <c r="R13" s="11" t="s">
+      <c r="R13" s="17"/>
+      <c r="S13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="S13" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D13:R13,"A")+COUNTIF(D13:R13,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D13:R13,"R")+COUNTIF(D13:R13,"A/R")=0,"Falta R","OK"))</f>
+      <c r="T13" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D13:S13,"A")+COUNTIF(D13:S13,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D13:S13,"R")+COUNTIF(D13:S13,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -4906,8 +4935,9 @@
       <c r="P14" s="17"/>
       <c r="Q14" s="17"/>
       <c r="R14" s="17"/>
-      <c r="S14" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D14:R14,"A")+COUNTIF(D14:R14,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D14:R14,"R")+COUNTIF(D14:R14,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S14" s="17"/>
+      <c r="T14" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D14:S14,"A")+COUNTIF(D14:S14,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D14:S14,"R")+COUNTIF(D14:S14,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -4941,15 +4971,16 @@
         <v>50</v>
       </c>
       <c r="M15" s="17"/>
-      <c r="N15" s="11" t="s">
+      <c r="N15" s="17"/>
+      <c r="O15" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="O15" s="17"/>
       <c r="P15" s="17"/>
       <c r="Q15" s="17"/>
       <c r="R15" s="17"/>
-      <c r="S15" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D15:R15,"A")+COUNTIF(D15:R15,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D15:R15,"R")+COUNTIF(D15:R15,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S15" s="17"/>
+      <c r="T15" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D15:S15,"A")+COUNTIF(D15:S15,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D15:S15,"R")+COUNTIF(D15:S15,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -4981,15 +5012,16 @@
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
-      <c r="N16" s="11" t="s">
+      <c r="N16" s="17"/>
+      <c r="O16" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="O16" s="17"/>
       <c r="P16" s="17"/>
       <c r="Q16" s="17"/>
       <c r="R16" s="17"/>
-      <c r="S16" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D16:R16,"A")+COUNTIF(D16:R16,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D16:R16,"R")+COUNTIF(D16:R16,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S16" s="17"/>
+      <c r="T16" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D16:S16,"A")+COUNTIF(D16:S16,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D16:S16,"R")+COUNTIF(D16:S16,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5019,15 +5051,16 @@
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
-      <c r="N17" s="11" t="s">
+      <c r="N17" s="17"/>
+      <c r="O17" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="O17" s="17"/>
       <c r="P17" s="17"/>
       <c r="Q17" s="17"/>
       <c r="R17" s="17"/>
-      <c r="S17" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D17:R17,"A")+COUNTIF(D17:R17,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D17:R17,"R")+COUNTIF(D17:R17,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S17" s="17"/>
+      <c r="T17" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D17:S17,"A")+COUNTIF(D17:S17,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D17:S17,"R")+COUNTIF(D17:S17,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5059,15 +5092,16 @@
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
-      <c r="N18" s="11" t="s">
+      <c r="N18" s="17"/>
+      <c r="O18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="O18" s="17"/>
       <c r="P18" s="17"/>
       <c r="Q18" s="17"/>
       <c r="R18" s="17"/>
-      <c r="S18" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D18:R18,"A")+COUNTIF(D18:R18,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D18:R18,"R")+COUNTIF(D18:R18,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S18" s="17"/>
+      <c r="T18" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D18:S18,"A")+COUNTIF(D18:S18,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D18:S18,"R")+COUNTIF(D18:S18,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5097,15 +5131,16 @@
       </c>
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
-      <c r="N19" s="11" t="s">
+      <c r="N19" s="17"/>
+      <c r="O19" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="O19" s="17"/>
       <c r="P19" s="17"/>
       <c r="Q19" s="17"/>
       <c r="R19" s="17"/>
-      <c r="S19" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D19:R19,"A")+COUNTIF(D19:R19,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D19:R19,"R")+COUNTIF(D19:R19,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S19" s="17"/>
+      <c r="T19" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D19:S19,"A")+COUNTIF(D19:S19,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D19:S19,"R")+COUNTIF(D19:S19,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5133,17 +5168,18 @@
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
-      <c r="N20" s="12" t="s">
+      <c r="N20" s="17"/>
+      <c r="O20" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="O20" s="17"/>
-      <c r="P20" s="10" t="s">
+      <c r="P20" s="17"/>
+      <c r="Q20" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="Q20" s="17"/>
       <c r="R20" s="17"/>
-      <c r="S20" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D20:R20,"A")+COUNTIF(D20:R20,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D20:R20,"R")+COUNTIF(D20:R20,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S20" s="17"/>
+      <c r="T20" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D20:S20,"A")+COUNTIF(D20:S20,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D20:S20,"R")+COUNTIF(D20:S20,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5171,17 +5207,18 @@
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
-      <c r="N21" s="11" t="s">
+      <c r="N21" s="17"/>
+      <c r="O21" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="O21" s="17"/>
-      <c r="P21" s="12" t="s">
+      <c r="P21" s="17"/>
+      <c r="Q21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="Q21" s="17"/>
       <c r="R21" s="17"/>
-      <c r="S21" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D21:R21,"A")+COUNTIF(D21:R21,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D21:R21,"R")+COUNTIF(D21:R21,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S21" s="17"/>
+      <c r="T21" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D21:S21,"A")+COUNTIF(D21:S21,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D21:S21,"R")+COUNTIF(D21:S21,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5212,18 +5249,19 @@
         <v>48</v>
       </c>
       <c r="L22" s="17"/>
-      <c r="M22" s="12" t="s">
+      <c r="M22" s="17"/>
+      <c r="N22" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="N22" s="11" t="s">
+      <c r="O22" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="O22" s="17"/>
       <c r="P22" s="17"/>
       <c r="Q22" s="17"/>
       <c r="R22" s="17"/>
-      <c r="S22" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D22:R22,"A")+COUNTIF(D22:R22,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D22:R22,"R")+COUNTIF(D22:R22,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S22" s="17"/>
+      <c r="T22" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D22:S22,"A")+COUNTIF(D22:S22,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D22:S22,"R")+COUNTIF(D22:S22,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5258,12 +5296,13 @@
       <c r="N23" s="17"/>
       <c r="O23" s="17"/>
       <c r="P23" s="17"/>
-      <c r="Q23" s="12" t="s">
+      <c r="Q23" s="17"/>
+      <c r="R23" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="R23" s="17"/>
-      <c r="S23" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D23:R23,"A")+COUNTIF(D23:R23,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D23:R23,"R")+COUNTIF(D23:R23,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S23" s="17"/>
+      <c r="T23" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D23:S23,"A")+COUNTIF(D23:S23,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D23:S23,"R")+COUNTIF(D23:S23,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5295,15 +5334,16 @@
         <v>48</v>
       </c>
       <c r="M24" s="17"/>
-      <c r="N24" s="12" t="s">
+      <c r="N24" s="17"/>
+      <c r="O24" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="O24" s="17"/>
       <c r="P24" s="17"/>
       <c r="Q24" s="17"/>
       <c r="R24" s="17"/>
-      <c r="S24" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D24:R24,"A")+COUNTIF(D24:R24,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D24:R24,"R")+COUNTIF(D24:R24,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S24" s="17"/>
+      <c r="T24" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D24:S24,"A")+COUNTIF(D24:S24,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D24:S24,"R")+COUNTIF(D24:S24,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5334,14 +5374,15 @@
       </c>
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
-      <c r="O25" s="12" t="s">
+      <c r="O25" s="17"/>
+      <c r="P25" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="P25" s="17"/>
       <c r="Q25" s="17"/>
       <c r="R25" s="17"/>
-      <c r="S25" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D25:R25,"A")+COUNTIF(D25:R25,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D25:R25,"R")+COUNTIF(D25:R25,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S25" s="17"/>
+      <c r="T25" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D25:S25,"A")+COUNTIF(D25:S25,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D25:S25,"R")+COUNTIF(D25:S25,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5374,12 +5415,13 @@
       <c r="N26" s="17"/>
       <c r="O26" s="17"/>
       <c r="P26" s="17"/>
-      <c r="Q26" s="11" t="s">
+      <c r="Q26" s="17"/>
+      <c r="R26" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="R26" s="17"/>
-      <c r="S26" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D26:R26,"A")+COUNTIF(D26:R26,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D26:R26,"R")+COUNTIF(D26:R26,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S26" s="17"/>
+      <c r="T26" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D26:S26,"A")+COUNTIF(D26:S26,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D26:S26,"R")+COUNTIF(D26:S26,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5408,18 +5450,19 @@
         <v>44</v>
       </c>
       <c r="L27" s="17"/>
-      <c r="M27" s="12" t="s">
+      <c r="M27" s="17"/>
+      <c r="N27" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="N27" s="17"/>
-      <c r="O27" s="11" t="s">
+      <c r="O27" s="17"/>
+      <c r="P27" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="P27" s="17"/>
       <c r="Q27" s="17"/>
       <c r="R27" s="17"/>
-      <c r="S27" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D27:R27,"A")+COUNTIF(D27:R27,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D27:R27,"R")+COUNTIF(D27:R27,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S27" s="17"/>
+      <c r="T27" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D27:S27,"A")+COUNTIF(D27:S27,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D27:S27,"R")+COUNTIF(D27:S27,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5450,18 +5493,19 @@
         <v>48</v>
       </c>
       <c r="L28" s="17"/>
-      <c r="M28" s="11" t="s">
+      <c r="M28" s="17"/>
+      <c r="N28" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N28" s="12" t="s">
+      <c r="O28" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="O28" s="17"/>
       <c r="P28" s="17"/>
       <c r="Q28" s="17"/>
       <c r="R28" s="17"/>
-      <c r="S28" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D28:R28,"A")+COUNTIF(D28:R28,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D28:R28,"R")+COUNTIF(D28:R28,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S28" s="17"/>
+      <c r="T28" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D28:S28,"A")+COUNTIF(D28:S28,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D28:S28,"R")+COUNTIF(D28:S28,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5490,16 +5534,17 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" s="17"/>
-      <c r="O29" s="12" t="s">
+      <c r="O29" s="17"/>
+      <c r="P29" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="P29" s="11" t="s">
+      <c r="Q29" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="Q29" s="17"/>
       <c r="R29" s="17"/>
-      <c r="S29" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D29:R29,"A")+COUNTIF(D29:R29,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D29:R29,"R")+COUNTIF(D29:R29,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S29" s="17"/>
+      <c r="T29" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D29:S29,"A")+COUNTIF(D29:S29,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D29:S29,"R")+COUNTIF(D29:S29,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5530,20 +5575,21 @@
       <c r="L30" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M30" s="12" t="s">
-        <v>50</v>
-      </c>
+      <c r="M30" s="17"/>
       <c r="N30" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="O30" s="11" t="s">
+      <c r="O30" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="P30" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="P30" s="17"/>
       <c r="Q30" s="17"/>
       <c r="R30" s="17"/>
-      <c r="S30" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D30:R30,"A")+COUNTIF(D30:R30,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D30:R30,"R")+COUNTIF(D30:R30,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S30" s="17"/>
+      <c r="T30" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D30:S30,"A")+COUNTIF(D30:S30,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D30:S30,"R")+COUNTIF(D30:S30,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5574,14 +5620,15 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" s="17"/>
-      <c r="O31" s="11" t="s">
+      <c r="O31" s="17"/>
+      <c r="P31" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="P31" s="17"/>
       <c r="Q31" s="17"/>
       <c r="R31" s="17"/>
-      <c r="S31" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D31:R31,"A")+COUNTIF(D31:R31,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D31:R31,"R")+COUNTIF(D31:R31,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S31" s="17"/>
+      <c r="T31" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D31:S31,"A")+COUNTIF(D31:S31,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D31:S31,"R")+COUNTIF(D31:S31,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5612,14 +5659,15 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" s="17"/>
-      <c r="O32" s="12" t="s">
+      <c r="O32" s="17"/>
+      <c r="P32" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="P32" s="17"/>
       <c r="Q32" s="17"/>
       <c r="R32" s="17"/>
-      <c r="S32" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D32:R32,"A")+COUNTIF(D32:R32,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D32:R32,"R")+COUNTIF(D32:R32,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S32" s="17"/>
+      <c r="T32" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D32:S32,"A")+COUNTIF(D32:S32,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D32:S32,"R")+COUNTIF(D32:S32,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5649,19 +5697,20 @@
       </c>
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
-      <c r="N33" s="12" t="s">
+      <c r="N33" s="17"/>
+      <c r="O33" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="O33" s="11" t="s">
+      <c r="P33" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="P33" s="17"/>
       <c r="Q33" s="17"/>
-      <c r="R33" s="11" t="s">
+      <c r="R33" s="17"/>
+      <c r="S33" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="S33" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D33:R33,"A")+COUNTIF(D33:R33,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D33:R33,"R")+COUNTIF(D33:R33,"A/R")=0,"Falta R","OK"))</f>
+      <c r="T33" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D33:S33,"A")+COUNTIF(D33:S33,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D33:S33,"R")+COUNTIF(D33:S33,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5690,16 +5739,17 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
-      <c r="O34" s="11" t="s">
+      <c r="O34" s="17"/>
+      <c r="P34" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="P34" s="17"/>
       <c r="Q34" s="17"/>
-      <c r="R34" s="11" t="s">
+      <c r="R34" s="17"/>
+      <c r="S34" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D34:R34,"A")+COUNTIF(D34:R34,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D34:R34,"R")+COUNTIF(D34:R34,"A/R")=0,"Falta R","OK"))</f>
+      <c r="T34" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D34:S34,"A")+COUNTIF(D34:S34,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D34:S34,"R")+COUNTIF(D34:S34,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5729,15 +5779,16 @@
       </c>
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
-      <c r="N35" s="12" t="s">
+      <c r="N35" s="17"/>
+      <c r="O35" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="O35" s="17"/>
       <c r="P35" s="17"/>
       <c r="Q35" s="17"/>
       <c r="R35" s="17"/>
-      <c r="S35" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D35:R35,"A")+COUNTIF(D35:R35,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D35:R35,"R")+COUNTIF(D35:R35,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S35" s="17"/>
+      <c r="T35" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D35:S35,"A")+COUNTIF(D35:S35,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D35:S35,"R")+COUNTIF(D35:S35,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5765,17 +5816,18 @@
       <c r="K36" s="17"/>
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
-      <c r="N36" s="12" t="s">
+      <c r="N36" s="17"/>
+      <c r="O36" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="O36" s="17"/>
-      <c r="P36" s="11" t="s">
+      <c r="P36" s="17"/>
+      <c r="Q36" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="Q36" s="17"/>
       <c r="R36" s="17"/>
-      <c r="S36" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D36:R36,"A")+COUNTIF(D36:R36,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D36:R36,"R")+COUNTIF(D36:R36,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S36" s="17"/>
+      <c r="T36" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D36:S36,"A")+COUNTIF(D36:S36,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D36:S36,"R")+COUNTIF(D36:S36,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5804,18 +5856,19 @@
         <v>48</v>
       </c>
       <c r="L37" s="17"/>
-      <c r="M37" s="12" t="s">
+      <c r="M37" s="17"/>
+      <c r="N37" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="N37" s="10" t="s">
+      <c r="O37" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="O37" s="17"/>
       <c r="P37" s="17"/>
       <c r="Q37" s="17"/>
       <c r="R37" s="17"/>
-      <c r="S37" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D37:R37,"A")+COUNTIF(D37:R37,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D37:R37,"R")+COUNTIF(D37:R37,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S37" s="17"/>
+      <c r="T37" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D37:S37,"A")+COUNTIF(D37:S37,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D37:S37,"R")+COUNTIF(D37:S37,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5843,17 +5896,18 @@
       <c r="K38" s="17"/>
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
-      <c r="N38" s="12" t="s">
+      <c r="N38" s="17"/>
+      <c r="O38" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="O38" s="17"/>
-      <c r="P38" s="10" t="s">
+      <c r="P38" s="17"/>
+      <c r="Q38" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="17"/>
       <c r="R38" s="17"/>
-      <c r="S38" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D38:R38,"A")+COUNTIF(D38:R38,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D38:R38,"R")+COUNTIF(D38:R38,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S38" s="17"/>
+      <c r="T38" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D38:S38,"A")+COUNTIF(D38:S38,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D38:S38,"R")+COUNTIF(D38:S38,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5882,18 +5936,19 @@
         <v>44</v>
       </c>
       <c r="L39" s="17"/>
-      <c r="M39" s="12" t="s">
+      <c r="M39" s="17"/>
+      <c r="N39" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="N39" s="17"/>
-      <c r="O39" s="11" t="s">
+      <c r="O39" s="17"/>
+      <c r="P39" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="P39" s="17"/>
       <c r="Q39" s="17"/>
       <c r="R39" s="17"/>
-      <c r="S39" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D39:R39,"A")+COUNTIF(D39:R39,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D39:R39,"R")+COUNTIF(D39:R39,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S39" s="17"/>
+      <c r="T39" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D39:S39,"A")+COUNTIF(D39:S39,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D39:S39,"R")+COUNTIF(D39:S39,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5922,18 +5977,19 @@
         <v>48</v>
       </c>
       <c r="L40" s="17"/>
-      <c r="M40" s="9" t="s">
+      <c r="M40" s="17"/>
+      <c r="N40" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="N40" s="17"/>
-      <c r="O40" s="10" t="s">
+      <c r="O40" s="17"/>
+      <c r="P40" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="P40" s="17"/>
       <c r="Q40" s="17"/>
       <c r="R40" s="17"/>
-      <c r="S40" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D40:R40,"A")+COUNTIF(D40:R40,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D40:R40,"R")+COUNTIF(D40:R40,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S40" s="17"/>
+      <c r="T40" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D40:S40,"A")+COUNTIF(D40:S40,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D40:S40,"R")+COUNTIF(D40:S40,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -5966,14 +6022,15 @@
       </c>
       <c r="M41" s="17"/>
       <c r="N41" s="17"/>
-      <c r="O41" s="11" t="s">
+      <c r="O41" s="17"/>
+      <c r="P41" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="P41" s="17"/>
       <c r="Q41" s="17"/>
       <c r="R41" s="17"/>
-      <c r="S41" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D41:R41,"A")+COUNTIF(D41:R41,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D41:R41,"R")+COUNTIF(D41:R41,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S41" s="17"/>
+      <c r="T41" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D41:S41,"A")+COUNTIF(D41:S41,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D41:S41,"R")+COUNTIF(D41:S41,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -6008,14 +6065,15 @@
       </c>
       <c r="M42" s="17"/>
       <c r="N42" s="17"/>
-      <c r="O42" s="11" t="s">
+      <c r="O42" s="17"/>
+      <c r="P42" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="P42" s="17"/>
       <c r="Q42" s="17"/>
       <c r="R42" s="17"/>
-      <c r="S42" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D42:R42,"A")+COUNTIF(D42:R42,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D42:R42,"R")+COUNTIF(D42:R42,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S42" s="17"/>
+      <c r="T42" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D42:S42,"A")+COUNTIF(D42:S42,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D42:S42,"R")+COUNTIF(D42:S42,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -6050,12 +6108,13 @@
       <c r="N43" s="17"/>
       <c r="O43" s="17"/>
       <c r="P43" s="17"/>
-      <c r="Q43" s="12" t="s">
+      <c r="Q43" s="17"/>
+      <c r="R43" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="R43" s="17"/>
-      <c r="S43" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D43:R43,"A")+COUNTIF(D43:R43,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D43:R43,"R")+COUNTIF(D43:R43,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S43" s="17"/>
+      <c r="T43" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D43:S43,"A")+COUNTIF(D43:S43,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D43:S43,"R")+COUNTIF(D43:S43,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -6085,17 +6144,18 @@
         <v>44</v>
       </c>
       <c r="M44" s="17"/>
-      <c r="N44" s="11" t="s">
+      <c r="N44" s="17"/>
+      <c r="O44" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="O44" s="17"/>
       <c r="P44" s="17"/>
-      <c r="Q44" s="11" t="s">
+      <c r="Q44" s="17"/>
+      <c r="R44" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="R44" s="17"/>
-      <c r="S44" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D44:R44,"A")+COUNTIF(D44:R44,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D44:R44,"R")+COUNTIF(D44:R44,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S44" s="17"/>
+      <c r="T44" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D44:S44,"A")+COUNTIF(D44:S44,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D44:S44,"R")+COUNTIF(D44:S44,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -6132,8 +6192,9 @@
       <c r="P45" s="17"/>
       <c r="Q45" s="17"/>
       <c r="R45" s="17"/>
-      <c r="S45" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D45:R45,"A")+COUNTIF(D45:R45,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D45:R45,"R")+COUNTIF(D45:R45,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S45" s="17"/>
+      <c r="T45" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D45:S45,"A")+COUNTIF(D45:S45,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D45:S45,"R")+COUNTIF(D45:S45,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -6165,15 +6226,16 @@
       <c r="M46" s="17"/>
       <c r="N46" s="17"/>
       <c r="O46" s="17"/>
-      <c r="P46" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="P46" s="17"/>
       <c r="Q46" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="R46" s="17"/>
-      <c r="S46" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D46:R46,"A")+COUNTIF(D46:R46,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D46:R46,"R")+COUNTIF(D46:R46,"A/R")=0,"Falta R","OK"))</f>
+      <c r="R46" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="S46" s="17"/>
+      <c r="T46" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D46:S46,"A")+COUNTIF(D46:S46,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D46:S46,"R")+COUNTIF(D46:S46,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -6203,17 +6265,18 @@
         <v>44</v>
       </c>
       <c r="M47" s="17"/>
-      <c r="N47" s="11" t="s">
+      <c r="N47" s="17"/>
+      <c r="O47" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="O47" s="17"/>
       <c r="P47" s="17"/>
-      <c r="Q47" s="11" t="s">
+      <c r="Q47" s="17"/>
+      <c r="R47" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="R47" s="17"/>
-      <c r="S47" s="18" t="str">
-        <f aca="false">IF(COUNTIF(D47:R47,"A")+COUNTIF(D47:R47,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D47:R47,"R")+COUNTIF(D47:R47,"A/R")=0,"Falta R","OK"))</f>
+      <c r="S47" s="17"/>
+      <c r="T47" s="18" t="str">
+        <f aca="false">IF(COUNTIF(D47:S47,"A")+COUNTIF(D47:S47,"A/R")&lt;&gt;1,"Revisar A",IF(COUNTIF(D47:S47,"R")+COUNTIF(D47:S47,"A/R")=0,"Falta R","OK"))</f>
         <v>OK</v>
       </c>
     </row>
@@ -6225,11 +6288,11 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="D2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:R47" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:S47" type="list">
       <formula1>"R,A,A/R,C,I"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6250,7 +6313,7 @@
     <tabColor rgb="FF98C9EB"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -6492,15 +6555,15 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>197</v>
+        <v>286</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>233</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>287</v>
@@ -6511,42 +6574,40 @@
       <c r="F11" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="G11" s="13" t="s">
-        <v>290</v>
-      </c>
+      <c r="G11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>291</v>
+        <v>197</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>234</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D12" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="F12" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="G12" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="G12" s="13" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
         <v>295</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>198</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>235</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>296</v>
@@ -6561,73 +6622,96 @@
         <v>299</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D14" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="G14" s="13" t="s">
         <v>301</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>237</v>
+        <v>128</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D15" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="F15" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="G15" s="13" t="s">
         <v>305</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B17" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="F16" s="13" t="s">
+      <c r="C17" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="E17" s="13" t="s">
         <v>311</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -6647,7 +6731,7 @@
     <tabColor rgb="FF98C9EB"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -6661,134 +6745,134 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>241</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>64</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D3" s="20"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>264</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>264</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D5" s="20"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>264</v>
+        <v>74</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D6" s="20"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>264</v>
+        <v>197</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="13"/>
       <c r="F7" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
@@ -6801,12 +6885,12 @@
         <v>102</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D8" s="20"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
@@ -6819,12 +6903,12 @@
         <v>111</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
@@ -6837,12 +6921,12 @@
         <v>103</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
@@ -6855,202 +6939,162 @@
         <v>237</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>331</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C12" s="20"/>
       <c r="D12" s="20"/>
       <c r="E12" s="13"/>
-      <c r="F12" s="13" t="s">
-        <v>332</v>
-      </c>
+      <c r="F12" s="13"/>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>331</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="C13" s="20"/>
       <c r="D13" s="20"/>
       <c r="E13" s="13"/>
-      <c r="F13" s="13" t="s">
-        <v>332</v>
-      </c>
+      <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>333</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C14" s="20"/>
       <c r="D14" s="20"/>
       <c r="E14" s="13"/>
-      <c r="F14" s="13" t="s">
-        <v>321</v>
-      </c>
+      <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>334</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C15" s="20"/>
       <c r="D15" s="20"/>
       <c r="E15" s="13"/>
-      <c r="F15" s="13" t="s">
-        <v>321</v>
-      </c>
+      <c r="F15" s="13"/>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>335</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C16" s="20"/>
       <c r="D16" s="20"/>
       <c r="E16" s="13"/>
-      <c r="F16" s="13" t="s">
-        <v>332</v>
-      </c>
+      <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>335</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="C17" s="20"/>
       <c r="D17" s="20"/>
       <c r="E17" s="13"/>
-      <c r="F17" s="13" t="s">
-        <v>336</v>
-      </c>
+      <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>335</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C18" s="20"/>
       <c r="D18" s="20"/>
       <c r="E18" s="13"/>
-      <c r="F18" s="13" t="s">
-        <v>329</v>
-      </c>
+      <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>337</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C19" s="20"/>
       <c r="D19" s="20"/>
       <c r="E19" s="13"/>
-      <c r="F19" s="13" t="s">
-        <v>321</v>
-      </c>
+      <c r="F19" s="13"/>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>338</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C20" s="20"/>
       <c r="D20" s="20"/>
       <c r="E20" s="13"/>
-      <c r="F20" s="13" t="s">
-        <v>321</v>
-      </c>
+      <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>339</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="C21" s="20"/>
       <c r="D21" s="20"/>
       <c r="E21" s="13"/>
-      <c r="F21" s="13" t="s">
-        <v>321</v>
-      </c>
+      <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="20"/>
@@ -7061,10 +7105,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20"/>
@@ -7075,10 +7119,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
@@ -7089,10 +7133,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="20"/>
@@ -7103,10 +7147,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
@@ -7117,10 +7161,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
@@ -7131,10 +7175,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="20"/>
@@ -7145,10 +7189,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="20"/>
@@ -7159,10 +7203,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
@@ -7173,10 +7217,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="20"/>
@@ -7187,147 +7231,205 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="20"/>
+        <v>237</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>338</v>
+      </c>
       <c r="D32" s="20"/>
       <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
+      <c r="F32" s="13" t="s">
+        <v>323</v>
+      </c>
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C33" s="20"/>
+        <v>237</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>339</v>
+      </c>
       <c r="D33" s="20"/>
       <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
+      <c r="F33" s="13" t="s">
+        <v>340</v>
+      </c>
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" s="20"/>
+        <v>139</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>339</v>
+      </c>
       <c r="D34" s="20"/>
       <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
+      <c r="F34" s="13" t="s">
+        <v>340</v>
+      </c>
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C35" s="20"/>
+        <v>295</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>341</v>
+      </c>
       <c r="D35" s="20"/>
       <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
+      <c r="F35" s="13" t="s">
+        <v>323</v>
+      </c>
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="20"/>
+        <v>264</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>342</v>
+      </c>
       <c r="D36" s="20"/>
       <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
+      <c r="F36" s="13" t="s">
+        <v>323</v>
+      </c>
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C37" s="20"/>
       <c r="D37" s="20"/>
       <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
+      <c r="F37" s="13" t="s">
+        <v>323</v>
+      </c>
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="B38" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" s="20"/>
       <c r="D38" s="20"/>
       <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
+      <c r="F38" s="13" t="s">
+        <v>340</v>
+      </c>
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" s="20"/>
       <c r="D39" s="20"/>
       <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
+      <c r="F39" s="13" t="s">
+        <v>345</v>
+      </c>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="B40" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" s="20"/>
       <c r="D40" s="20"/>
       <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
+      <c r="F40" s="13" t="s">
+        <v>331</v>
+      </c>
       <c r="G40" s="13"/>
       <c r="H40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C41" s="20"/>
+        <v>286</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>346</v>
+      </c>
       <c r="D41" s="20"/>
       <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
+      <c r="F41" s="13" t="s">
+        <v>323</v>
+      </c>
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="19" t="s">
-        <v>345</v>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="D42" s="20"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="19" t="s">
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -7347,7 +7449,7 @@
     <tabColor rgb="FF98C9EB"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -7365,60 +7467,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C2" s="21" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G2" s="21" t="s">
         <v>64</v>
@@ -7431,27 +7533,27 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C3" s="21" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G3" s="21"/>
       <c r="H3" s="21"/>
       <c r="I3" s="21" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="J3" s="21"/>
       <c r="K3" s="21"/>
@@ -7459,29 +7561,29 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C4" s="21" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>361</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>358</v>
       </c>
       <c r="G4" s="21" t="s">
         <v>65</v>
       </c>
       <c r="H4" s="21"/>
       <c r="I4" s="21" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="J4" s="21"/>
       <c r="K4" s="21"/>
@@ -7489,29 +7591,29 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C5" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>324</v>
+        <v>367</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G5" s="21" t="s">
         <v>264</v>
       </c>
       <c r="H5" s="21"/>
       <c r="I5" s="21" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
@@ -7519,29 +7621,29 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C6" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G6" s="21" t="s">
         <v>264</v>
       </c>
       <c r="H6" s="21"/>
       <c r="I6" s="21" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
@@ -7549,25 +7651,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
       <c r="I7" s="13" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
@@ -7575,25 +7677,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
       <c r="I8" s="13" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
@@ -7601,22 +7703,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
@@ -7627,29 +7729,29 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C10" s="21" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="E10" s="23" t="s">
         <v>371</v>
       </c>
-      <c r="E10" s="23" t="s">
-        <v>367</v>
-      </c>
       <c r="F10" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G10" s="21" t="s">
         <v>64</v>
       </c>
       <c r="H10" s="21"/>
       <c r="I10" s="21" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21"/>
@@ -7657,22 +7759,22 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C11" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G11" s="21" t="s">
         <v>65</v>
@@ -7687,22 +7789,22 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C12" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G12" s="21" t="s">
         <v>91</v>
@@ -7717,22 +7819,22 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C13" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G13" s="21" t="s">
         <v>74</v>
@@ -7747,22 +7849,22 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C14" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G14" s="21" t="s">
         <v>264</v>
@@ -7777,29 +7879,29 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C15" s="21" t="n">
         <v>4</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G15" s="21" t="s">
         <v>264</v>
       </c>
       <c r="H15" s="21"/>
       <c r="I15" s="21" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21"/>
@@ -7807,22 +7909,22 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C16" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G16" s="21" t="s">
         <v>102</v>
@@ -7834,7 +7936,7 @@
       <c r="J16" s="21"/>
       <c r="K16" s="21"/>
       <c r="L16" s="21" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7842,114 +7944,116 @@
         <v>327</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E17" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="H17" s="13"/>
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>356</v>
-      </c>
-      <c r="C18" s="21" t="n">
+      <c r="B18" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="C18" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>381</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G18" s="21" t="s">
+      <c r="D18" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G19" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
         <v>327</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
@@ -7960,26 +8064,26 @@
         <v>327</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>237</v>
+        <v>295</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="13" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
@@ -7990,16 +8094,16 @@
         <v>327</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>237</v>
@@ -8020,26 +8124,26 @@
         <v>327</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>390</v>
+        <v>339</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="13" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
@@ -8050,26 +8154,26 @@
         <v>327</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>198</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="13" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
@@ -8080,118 +8184,118 @@
         <v>327</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>367</v>
+        <v>396</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>347</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>370</v>
+        <v>233</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="I25" s="13"/>
+        <v>198</v>
+      </c>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13" t="s">
+        <v>397</v>
+      </c>
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
-      <c r="L25" s="13" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
+      <c r="L25" s="13"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B26" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C26" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G26" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21" t="s">
+      <c r="B26" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="J26" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E26" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
         <v>327</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C27" s="21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="H27" s="21"/>
       <c r="I27" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="J27" s="21"/>
+        <v>64</v>
+      </c>
+      <c r="J27" s="21" t="s">
+        <v>197</v>
+      </c>
       <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
+      <c r="L27" s="21" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
         <v>327</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C28" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H28" s="21"/>
       <c r="I28" s="21" t="s">
@@ -8206,22 +8310,22 @@
         <v>327</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C29" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="H29" s="21"/>
       <c r="I29" s="21" t="s">
@@ -8232,150 +8336,150 @@
       <c r="L29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>367</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
+      <c r="B30" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C30" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>64</v>
+        <v>197</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>319</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="H31" s="13"/>
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
       <c r="K31" s="13"/>
-      <c r="L31" s="13" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
-        <v>340</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C32" s="21" t="n">
+      <c r="L31" s="13"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C33" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G32" s="21" t="s">
+      <c r="D33" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G33" s="21" t="s">
         <v>102</v>
-      </c>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="J32" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21" t="s">
-        <v>340</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C33" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G33" s="21" t="s">
-        <v>111</v>
       </c>
       <c r="H33" s="21"/>
       <c r="I33" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="J33" s="21"/>
+        <v>64</v>
+      </c>
+      <c r="J33" s="21" t="s">
+        <v>197</v>
+      </c>
       <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="L33" s="21" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C34" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H34" s="21"/>
       <c r="I34" s="21" t="s">
@@ -8387,25 +8491,25 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C35" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G35" s="21" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="H35" s="21"/>
       <c r="I35" s="21" t="s">
@@ -8416,150 +8520,150 @@
       <c r="L35" s="21"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="C36" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>367</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="G36" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
+      <c r="A36" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C36" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>64</v>
+        <v>197</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>319</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="H37" s="13"/>
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
-      <c r="L37" s="13" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C38" s="21" t="n">
+      <c r="L37" s="13"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C39" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F38" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G38" s="21" t="s">
+      <c r="D39" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G39" s="21" t="s">
         <v>102</v>
-      </c>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="J38" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C39" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G39" s="21" t="s">
-        <v>111</v>
       </c>
       <c r="H39" s="21"/>
       <c r="I39" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="J39" s="21"/>
+        <v>64</v>
+      </c>
+      <c r="J39" s="21" t="s">
+        <v>197</v>
+      </c>
       <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
+      <c r="L39" s="21" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C40" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G40" s="21" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H40" s="21"/>
       <c r="I40" s="21" t="s">
@@ -8571,25 +8675,25 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C41" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G41" s="21" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="H41" s="21"/>
       <c r="I41" s="21" t="s">
@@ -8600,150 +8704,150 @@
       <c r="L41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="C42" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="E42" s="22" t="s">
-        <v>367</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
-      <c r="L42" s="13"/>
+      <c r="A42" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C42" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="F42" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J42" s="21"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="21"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C43" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>64</v>
+        <v>197</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>319</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="H43" s="13"/>
       <c r="I43" s="13"/>
       <c r="J43" s="13"/>
       <c r="K43" s="13"/>
-      <c r="L43" s="13" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C44" s="21" t="n">
+      <c r="L43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C45" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D44" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F44" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G44" s="21" t="s">
+      <c r="D45" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G45" s="21" t="s">
         <v>102</v>
-      </c>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="J44" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="K44" s="21"/>
-      <c r="L44" s="21" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C45" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G45" s="21" t="s">
-        <v>111</v>
       </c>
       <c r="H45" s="21"/>
       <c r="I45" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="J45" s="21"/>
+        <v>64</v>
+      </c>
+      <c r="J45" s="21" t="s">
+        <v>197</v>
+      </c>
       <c r="K45" s="21"/>
-      <c r="L45" s="21"/>
+      <c r="L45" s="21" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C46" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G46" s="21" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H46" s="21"/>
       <c r="I46" s="21" t="s">
@@ -8755,25 +8859,25 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C47" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G47" s="21" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="H47" s="21"/>
       <c r="I47" s="21" t="s">
@@ -8784,150 +8888,150 @@
       <c r="L47" s="21"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="C48" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>367</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="G48" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
-      <c r="L48" s="13"/>
+      <c r="A48" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C48" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G48" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H48" s="21"/>
+      <c r="I48" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J48" s="21"/>
+      <c r="K48" s="21"/>
+      <c r="L48" s="21"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>64</v>
+        <v>197</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H49" s="13" t="s">
-        <v>319</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="H49" s="13"/>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
       <c r="K49" s="13"/>
-      <c r="L49" s="13" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C50" s="21" t="n">
+      <c r="L49" s="13"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C51" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D50" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F50" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G50" s="21" t="s">
+      <c r="D51" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G51" s="21" t="s">
         <v>102</v>
-      </c>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="J50" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="K50" s="21"/>
-      <c r="L50" s="21" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C51" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F51" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G51" s="21" t="s">
-        <v>111</v>
       </c>
       <c r="H51" s="21"/>
       <c r="I51" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="J51" s="21"/>
+        <v>64</v>
+      </c>
+      <c r="J51" s="21" t="s">
+        <v>197</v>
+      </c>
       <c r="K51" s="21"/>
-      <c r="L51" s="21"/>
+      <c r="L51" s="21" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C52" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G52" s="21" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H52" s="21"/>
       <c r="I52" s="21" t="s">
@@ -8939,25 +9043,25 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="21" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C53" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="H53" s="21"/>
       <c r="I53" s="21" t="s">
@@ -8968,150 +9072,150 @@
       <c r="L53" s="21"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="C54" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>367</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="K54" s="13"/>
-      <c r="L54" s="13"/>
+      <c r="A54" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C54" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="E54" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G54" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C55" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>64</v>
+        <v>197</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>319</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="H55" s="13"/>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
       <c r="K55" s="13"/>
-      <c r="L55" s="13" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="21" t="s">
-        <v>344</v>
-      </c>
-      <c r="B56" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C56" s="21" t="n">
+      <c r="L55" s="13"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C56" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H56" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C57" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D56" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="E56" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F56" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G56" s="21" t="s">
+      <c r="D57" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G57" s="21" t="s">
         <v>102</v>
-      </c>
-      <c r="H56" s="21"/>
-      <c r="I56" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="J56" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="K56" s="21"/>
-      <c r="L56" s="21" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="21" t="s">
-        <v>344</v>
-      </c>
-      <c r="B57" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C57" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="E57" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F57" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="G57" s="21" t="s">
-        <v>111</v>
       </c>
       <c r="H57" s="21"/>
       <c r="I57" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="J57" s="21"/>
+        <v>64</v>
+      </c>
+      <c r="J57" s="21" t="s">
+        <v>197</v>
+      </c>
       <c r="K57" s="21"/>
-      <c r="L57" s="21"/>
+      <c r="L57" s="21" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C58" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G58" s="21" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H58" s="21"/>
       <c r="I58" s="21" t="s">
@@ -9123,25 +9227,25 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="21" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C59" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F59" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G59" s="21" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="H59" s="21"/>
       <c r="I59" s="21" t="s">
@@ -9152,35 +9256,65 @@
       <c r="L59" s="21"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="C60" s="13" t="n">
+      <c r="A60" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C60" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="E60" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G60" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H60" s="21"/>
+      <c r="I60" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
+      <c r="L60" s="21"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C61" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D61" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E60" s="22" t="s">
-        <v>367</v>
-      </c>
-      <c r="F60" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="G60" s="13" t="s">
+      <c r="E61" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="F61" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="G61" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L60"/>
+  <autoFilter ref="A1:L61"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -9214,51 +9348,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>247</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="H2" s="13" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="I2" s="13"/>
     </row>
@@ -9267,124 +9401,124 @@
         <v>327</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
       <c r="H3" s="13" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="I4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
       <c r="H5" s="13" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="I5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="I6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="I7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="I8" s="13"/>
     </row>
@@ -9417,197 +9551,197 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>91</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>65</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>74</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>64</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13" t="s">
         <v>64</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>74</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>65</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>64</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>65</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13" t="s">
         <v>91</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F11" s="13"/>
     </row>
@@ -9642,36 +9776,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>73</v>
@@ -9684,13 +9818,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>84</v>
@@ -9703,13 +9837,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>84</v>
@@ -9722,13 +9856,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>73</v>
@@ -9741,13 +9875,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>84</v>
@@ -9760,13 +9894,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>84</v>
@@ -9779,13 +9913,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>84</v>
@@ -9798,13 +9932,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>84</v>
@@ -9817,13 +9951,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>73</v>
@@ -9836,13 +9970,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>84</v>
@@ -9855,13 +9989,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>73</v>
@@ -9874,13 +10008,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>69</v>
